--- a/technology_surveys/021_smartphone_consumer_behavior_quiz--technology_surveys.xlsx
+++ b/technology_surveys/021_smartphone_consumer_behavior_quiz--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'male'}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'female'}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Extra Large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'ios'}</t>
+          <t>ios</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'iOS'}</t>
+          <t>iOS</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'0-10'}</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': '0-10'}</t>
+          <t>0-10</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'10-20'}</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': '10-20'}</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'20-50'}</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': '20-50'}</t>
+          <t>20-50</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'more_than_50'}</t>
+          <t>more_than_50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'More than 50'}</t>
+          <t>More than 50</t>
         </is>
       </c>
     </row>
